--- a/base_bps.xlsx
+++ b/base_bps.xlsx
@@ -13327,17 +13327,17 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),6128.0)</f>
         <v>6128</v>
       </c>
-      <c r="F384" s="7" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"  ")</f>
-        <v/>
-      </c>
-      <c r="G384" s="6" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
-        <v/>
-      </c>
-      <c r="H384" s="7" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"  ")</f>
-        <v/>
+      <c r="F384" s="7">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5325.01)</f>
+        <v>5325.01</v>
+      </c>
+      <c r="G384" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),117.0)</f>
+        <v>117</v>
+      </c>
+      <c r="H384" s="7">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),45.512905982905984)</f>
+        <v>45.51290598</v>
       </c>
     </row>
     <row r="385">

--- a/base_bps.xlsx
+++ b/base_bps.xlsx
@@ -13361,17 +13361,17 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5896.46)</f>
         <v>5896.46</v>
       </c>
-      <c r="F385" s="7" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"  ")</f>
-        <v/>
-      </c>
-      <c r="G385" s="6" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
-        <v/>
-      </c>
-      <c r="H385" s="7" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"  ")</f>
-        <v/>
+      <c r="F385" s="7">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5553.01)</f>
+        <v>5553.01</v>
+      </c>
+      <c r="G385" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),126.0)</f>
+        <v>126</v>
+      </c>
+      <c r="H385" s="7">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),44.071507936507935)</f>
+        <v>44.07150794</v>
       </c>
     </row>
     <row r="386">

--- a/base_bps.xlsx
+++ b/base_bps.xlsx
@@ -13395,17 +13395,17 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),6145.1)</f>
         <v>6145.1</v>
       </c>
-      <c r="F386" s="7" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"  ")</f>
-        <v/>
-      </c>
-      <c r="G386" s="6" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
-        <v/>
-      </c>
-      <c r="H386" s="7" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"  ")</f>
-        <v/>
+      <c r="F386" s="7">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5663.0)</f>
+        <v>5663</v>
+      </c>
+      <c r="G386" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),110.0)</f>
+        <v>110</v>
+      </c>
+      <c r="H386" s="7">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),51.481818181818184)</f>
+        <v>51.48181818</v>
       </c>
     </row>
     <row r="387">

--- a/base_bps.xlsx
+++ b/base_bps.xlsx
@@ -13395,17 +13395,17 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),6145.1)</f>
         <v>6145.1</v>
       </c>
-      <c r="F386" s="7" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"  ")</f>
-        <v/>
-      </c>
-      <c r="G386" s="6" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
-        <v/>
-      </c>
-      <c r="H386" s="7" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"  ")</f>
-        <v/>
+      <c r="F386" s="7">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5663.0)</f>
+        <v>5663</v>
+      </c>
+      <c r="G386" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),110.0)</f>
+        <v>110</v>
+      </c>
+      <c r="H386" s="7">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),51.481818181818184)</f>
+        <v>51.48181818</v>
       </c>
     </row>
     <row r="387">
@@ -13429,17 +13429,17 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5931.27)</f>
         <v>5931.27</v>
       </c>
-      <c r="F387" s="7" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"  ")</f>
-        <v/>
-      </c>
-      <c r="G387" s="6" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
-        <v/>
-      </c>
-      <c r="H387" s="7" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"  ")</f>
-        <v/>
+      <c r="F387" s="7">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),6482.0)</f>
+        <v>6482</v>
+      </c>
+      <c r="G387" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),148.0)</f>
+        <v>148</v>
+      </c>
+      <c r="H387" s="7">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),43.7972972972973)</f>
+        <v>43.7972973</v>
       </c>
     </row>
     <row r="388">

--- a/base_bps.xlsx
+++ b/base_bps.xlsx
@@ -13429,17 +13429,17 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5931.27)</f>
         <v>5931.27</v>
       </c>
-      <c r="F387" s="7" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"  ")</f>
-        <v/>
-      </c>
-      <c r="G387" s="6" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
-        <v/>
-      </c>
-      <c r="H387" s="7" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"  ")</f>
-        <v/>
+      <c r="F387" s="7">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),6482.0)</f>
+        <v>6482</v>
+      </c>
+      <c r="G387" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),148.0)</f>
+        <v>148</v>
+      </c>
+      <c r="H387" s="7">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),43.7972972972973)</f>
+        <v>43.7972973</v>
       </c>
     </row>
     <row r="388">
@@ -13463,17 +13463,17 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),6255.94)</f>
         <v>6255.94</v>
       </c>
-      <c r="F388" s="7" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"  ")</f>
-        <v/>
-      </c>
-      <c r="G388" s="6" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
-        <v/>
-      </c>
-      <c r="H388" s="7" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"  ")</f>
-        <v/>
+      <c r="F388" s="7">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5394.0)</f>
+        <v>5394</v>
+      </c>
+      <c r="G388" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),116.0)</f>
+        <v>116</v>
+      </c>
+      <c r="H388" s="7">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),46.5)</f>
+        <v>46.5</v>
       </c>
     </row>
     <row r="389">

--- a/base_bps.xlsx
+++ b/base_bps.xlsx
@@ -13497,17 +13497,17 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),6348.41)</f>
         <v>6348.41</v>
       </c>
-      <c r="F389" s="7" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"  ")</f>
-        <v/>
-      </c>
-      <c r="G389" s="6" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
-        <v/>
-      </c>
-      <c r="H389" s="7" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"  ")</f>
-        <v/>
+      <c r="F389" s="7">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),7535.51)</f>
+        <v>7535.51</v>
+      </c>
+      <c r="G389" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),151.0)</f>
+        <v>151</v>
+      </c>
+      <c r="H389" s="7">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),49.90403973509934)</f>
+        <v>49.90403974</v>
       </c>
     </row>
     <row r="390">

--- a/base_bps.xlsx
+++ b/base_bps.xlsx
@@ -13531,17 +13531,17 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),7476.84)</f>
         <v>7476.84</v>
       </c>
-      <c r="F390" s="7" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"  ")</f>
-        <v/>
-      </c>
-      <c r="G390" s="6" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
-        <v/>
-      </c>
-      <c r="H390" s="7" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"  ")</f>
-        <v/>
+      <c r="F390" s="7">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),7588.0)</f>
+        <v>7588</v>
+      </c>
+      <c r="G390" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),159.0)</f>
+        <v>159</v>
+      </c>
+      <c r="H390" s="7">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),47.723270440251575)</f>
+        <v>47.72327044</v>
       </c>
     </row>
     <row r="391">

--- a/base_bps.xlsx
+++ b/base_bps.xlsx
@@ -13565,17 +13565,17 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),6128.0)</f>
         <v>6128</v>
       </c>
-      <c r="F391" s="7" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"  ")</f>
-        <v/>
-      </c>
-      <c r="G391" s="6" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
-        <v/>
-      </c>
-      <c r="H391" s="7" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"  ")</f>
-        <v/>
+      <c r="F391" s="7">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5265.5)</f>
+        <v>5265.5</v>
+      </c>
+      <c r="G391" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),113.0)</f>
+        <v>113</v>
+      </c>
+      <c r="H391" s="7">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),46.597345132743364)</f>
+        <v>46.59734513</v>
       </c>
     </row>
     <row r="392">

--- a/base_bps.xlsx
+++ b/base_bps.xlsx
@@ -13565,17 +13565,17 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),6128.0)</f>
         <v>6128</v>
       </c>
-      <c r="F391" s="7" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"  ")</f>
-        <v/>
-      </c>
-      <c r="G391" s="6" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
-        <v/>
-      </c>
-      <c r="H391" s="7" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"  ")</f>
-        <v/>
+      <c r="F391" s="7">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5265.5)</f>
+        <v>5265.5</v>
+      </c>
+      <c r="G391" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),113.0)</f>
+        <v>113</v>
+      </c>
+      <c r="H391" s="7">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),46.597345132743364)</f>
+        <v>46.59734513</v>
       </c>
     </row>
     <row r="392">
@@ -13599,17 +13599,17 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5896.46)</f>
         <v>5896.46</v>
       </c>
-      <c r="F392" s="7" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"  ")</f>
-        <v/>
-      </c>
-      <c r="G392" s="6" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
-        <v/>
-      </c>
-      <c r="H392" s="7" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"  ")</f>
-        <v/>
+      <c r="F392" s="7">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5575.0)</f>
+        <v>5575</v>
+      </c>
+      <c r="G392" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),136.0)</f>
+        <v>136</v>
+      </c>
+      <c r="H392" s="7">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),40.99264705882353)</f>
+        <v>40.99264706</v>
       </c>
     </row>
     <row r="393">

--- a/base_bps.xlsx
+++ b/base_bps.xlsx
@@ -13633,17 +13633,17 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),6145.1)</f>
         <v>6145.1</v>
       </c>
-      <c r="F393" s="7" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"  ")</f>
-        <v/>
-      </c>
-      <c r="G393" s="6" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
-        <v/>
-      </c>
-      <c r="H393" s="7" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"  ")</f>
-        <v/>
+      <c r="F393" s="7">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5777.0)</f>
+        <v>5777</v>
+      </c>
+      <c r="G393" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),130.0)</f>
+        <v>130</v>
+      </c>
+      <c r="H393" s="7">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),44.43846153846154)</f>
+        <v>44.43846154</v>
       </c>
     </row>
     <row r="394">

--- a/base_bps.xlsx
+++ b/base_bps.xlsx
@@ -13667,17 +13667,17 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5931.27)</f>
         <v>5931.27</v>
       </c>
-      <c r="F394" s="7" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"  ")</f>
-        <v/>
-      </c>
-      <c r="G394" s="6" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
-        <v/>
-      </c>
-      <c r="H394" s="7" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"  ")</f>
-        <v/>
+      <c r="F394" s="7">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5705.01)</f>
+        <v>5705.01</v>
+      </c>
+      <c r="G394" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),133.0)</f>
+        <v>133</v>
+      </c>
+      <c r="H394" s="7">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),42.89481203007519)</f>
+        <v>42.89481203</v>
       </c>
     </row>
     <row r="395">

--- a/base_bps.xlsx
+++ b/base_bps.xlsx
@@ -13701,17 +13701,17 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),6255.94)</f>
         <v>6255.94</v>
       </c>
-      <c r="F395" s="7" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"  ")</f>
-        <v/>
-      </c>
-      <c r="G395" s="6" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
-        <v/>
-      </c>
-      <c r="H395" s="7" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"  ")</f>
-        <v/>
+      <c r="F395" s="7">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5861.01)</f>
+        <v>5861.01</v>
+      </c>
+      <c r="G395" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),125.0)</f>
+        <v>125</v>
+      </c>
+      <c r="H395" s="7">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),46.88808)</f>
+        <v>46.88808</v>
       </c>
     </row>
     <row r="396">

--- a/base_bps.xlsx
+++ b/base_bps.xlsx
@@ -13735,17 +13735,17 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),6348.41)</f>
         <v>6348.41</v>
       </c>
-      <c r="F396" s="7" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"  ")</f>
-        <v/>
-      </c>
-      <c r="G396" s="6" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
-        <v/>
-      </c>
-      <c r="H396" s="7" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"  ")</f>
-        <v/>
+      <c r="F396" s="7">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),6144.0)</f>
+        <v>6144</v>
+      </c>
+      <c r="G396" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),140.0)</f>
+        <v>140</v>
+      </c>
+      <c r="H396" s="7">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),43.885714285714286)</f>
+        <v>43.88571429</v>
       </c>
     </row>
     <row r="397">

--- a/base_bps.xlsx
+++ b/base_bps.xlsx
@@ -13769,17 +13769,17 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),7476.84)</f>
         <v>7476.84</v>
       </c>
-      <c r="F397" s="7" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"  ")</f>
-        <v/>
-      </c>
-      <c r="G397" s="6" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
-        <v/>
-      </c>
-      <c r="H397" s="7" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"  ")</f>
-        <v/>
+      <c r="F397" s="7">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),6656.02)</f>
+        <v>6656.02</v>
+      </c>
+      <c r="G397" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),144.0)</f>
+        <v>144</v>
+      </c>
+      <c r="H397" s="7">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),46.22236111111111)</f>
+        <v>46.22236111</v>
       </c>
     </row>
     <row r="398">
